--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0231.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0231.xlsx
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Sự kiện chưa bắt đầu.</t>
+          <t>Sự kiện chưa bắt đầu đâu.</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Bạn chưa chọn Cộng Hưởng Giả 5 sao nào. Tiếp tục chọn chứ?</t>
+          <t>Bạn chưa chọn Resonator 5 sao nào. Tiếp tục chọn chứ?</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Xác nhận chọn Cộng Hưởng Giả 5 sao {0}.</t>
+          <t>Xác nhận chọn Resonator 5 sao {0}.</t>
         </is>
       </c>
     </row>
@@ -6359,7 +6359,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Sự kiện Triệu Tập hiện tại đã kết thúc.</t>
+          <t>Sự kiện Convene hiện tại đã kết thúc.</t>
         </is>
       </c>
     </row>
@@ -7204,7 +7204,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Sự kiện chưa bắt đầu.</t>
+          <t>Sự kiện chưa bắt đầu đâu.</t>
         </is>
       </c>
     </row>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Ta đã nói với {0}: {1}</t>
+          <t>Tao đã nói với {0}: {1}</t>
         </is>
       </c>
     </row>
@@ -12148,7 +12148,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Sự kiện chưa bắt đầu.</t>
+          <t>Sự kiện chưa bắt đầu đâu.</t>
         </is>
       </c>
     </row>
@@ -16438,7 +16438,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Cậu có thể nhận "Phiếu Đổi Giao Hưởng" qua &lt;color=#c19f51&gt;in-game mail&lt;/color&gt;.</t>
+          <t>Cậu có thể nhận "Phiếu Đổi Giao Hưởng" qua &lt;color=#c19f51&gt;thư trong game&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -18000,7 +18000,7 @@
       <c r="M270" t="inlineStr">
         <is>
           <t>Đã phát hiện bộ điều khiển. Chuyển sang Chế Độ Điều Khiển?
-(Bạn có thể chuyển đổi thủ công trong &lt;color=HighlightB&gt;Settings&lt;/color&gt; - &lt;color=HighlightB&gt;Key Bindings&lt;/color&gt;)</t>
+(Bạn có thể chuyển đổi thủ công trong &lt;color=HighlightB&gt;Cài Đặt&lt;/color&gt; - &lt;color=HighlightB&gt;Gán Phím&lt;/color&gt;)</t>
         </is>
       </c>
     </row>
@@ -18520,7 +18520,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>R?i ?i à?</t>
+          <t>Cút đi à?</t>
         </is>
       </c>
     </row>
@@ -18845,7 +18845,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Bạn chưa sở hữu Cộng Hưởng Giả này. Bạn sẽ không thể trang bị skin này sau khi mua. Vẫn muốn mua chứ?</t>
+          <t>Bạn chưa sở hữu Resonator này. Bạn sẽ không thể trang bị skin này sau khi mua. Vẫn muốn mua chứ?</t>
         </is>
       </c>
     </row>
@@ -19107,7 +19107,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Bạn chưa sở hữu Cộng Hưởng Giả này. Hãy thử lại sau khi có được Cộng Hưởng Giả này nhé.</t>
+          <t>Bạn chưa sở hữu Resonator này. Hãy thử lại sau khi có được Resonator này nhé.</t>
         </is>
       </c>
     </row>
@@ -19822,7 +19822,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Thu thập {0} Bộ Dữ liệu Giám sát</t>
+          <t>Thu thập {0} Bộ Dữ Liệu Giám Sát</t>
         </is>
       </c>
     </row>
@@ -21577,7 +21577,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Không thể tiến hành khi có Cộng Hưởng Giả thử nghiệm. Vui lòng hoàn thành nhiệm vụ hoặc sự kiện liên quan rồi thử lại.</t>
+          <t>Không thể tiến hành khi có Resonator thử nghiệm. Vui lòng hoàn thành nhiệm vụ hoặc sự kiện liên quan rồi thử lại.</t>
         </is>
       </c>
     </row>
@@ -23072,7 +23072,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Đang dùng Cộng Hưởng Giả thử nghiệm, không thể tham gia Hợp Tác.</t>
+          <t>Đang dùng Resonator thử nghiệm, không thể tham gia Hợp Tác.</t>
         </is>
       </c>
     </row>
@@ -24047,7 +24047,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Phát hiện Cộng Hưởng Giả trùng lặp trong Đội I và Đội II</t>
+          <t>Phát hiện Resonator trùng lặp trong Đội I và Đội II</t>
         </is>
       </c>
     </row>
@@ -24307,7 +24307,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Sự kiện chưa bắt đầu.</t>
+          <t>Sự kiện chưa bắt đầu đâu.</t>
         </is>
       </c>
     </row>
@@ -24437,7 +24437,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Sự kiện chưa bắt đầu.</t>
+          <t>Sự kiện chưa bắt đầu đâu.</t>
         </is>
       </c>
     </row>
@@ -24632,7 +24632,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Không thể thay đổi ngoại hình của Rover khi có Cộng Hưởng Giả thử nghiệm trong đội</t>
+          <t>Không thể thay đổi ngoại hình của Rover khi có Resonator thử nghiệm trong đội</t>
         </is>
       </c>
     </row>
@@ -25282,7 +25282,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Một số Echo đã được Cộng Hưởng Giả khác trang bị. Tiếp tục chứ?</t>
+          <t>Một số Echo đã được Resonator khác trang bị. Tiếp tục chứ?</t>
         </is>
       </c>
     </row>
@@ -30157,7 +30157,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Di chuyển Nhanh đến bến tàu? (Hàng hóa của cậu sẽ không bị bỏ lại)</t>
+          <t>Dịch chuyển Nhanh đến bến tàu? (Hàng hóa của cậu sẽ không bị bỏ lại)</t>
         </is>
       </c>
     </row>
@@ -31067,7 +31067,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Rover trong bản ghi này có giới tính khác. Không thể tiếp tục thử thách.</t>
+          <t>Vận Mệnh Giả trong bản ghi này có giới tính khác. Không thể tiếp tục thử thách.</t>
         </is>
       </c>
     </row>
@@ -31132,7 +31132,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Rover đang ở trong Cổng Ngàn Ảo Ảnh. Không thể thay đổi giới tính.</t>
+          <t>Vận Mệnh Giả đang ở trong Cổng Ngàn Ảo Ảnh. Không thể thay đổi giới tính.</t>
         </is>
       </c>
     </row>
@@ -31327,7 +31327,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Cộng Hưởng Giả này đã có trong đội. Vui lòng chọn Cộng Hưởng Giả khác và thử lại.</t>
+          <t>Resonator này đã có trong đội. Vui lòng chọn Resonator khác và thử lại.</t>
         </is>
       </c>
     </row>
@@ -31392,7 +31392,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Rover đã có trong đội rồi. Hãy chọn một Cộng Hưởng Giả khác và thử lại.</t>
+          <t>Rover đã có trong đội rồi. Hãy chọn một Resonator khác và thử lại.</t>
         </is>
       </c>
     </row>
@@ -32954,7 +32954,7 @@
       <c r="M500" t="inlineStr">
         <is>
           <t>Bạn có muốn tiếp tục từ tiến trình đã lưu trước đó không?
-&lt;color=#ac8839&gt;Starting over will erase your current progress&lt;/color&gt;</t>
+&lt;color=#ac8839&gt;Bắt đầu lại sẽ xóa tiến trình hiện tại của bạn&lt;/color&gt;</t>
         </is>
       </c>
     </row>
